--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824B08BC-82CE-42B4-80F3-1F3B80C4BED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88199344-6D9C-45B5-B9E0-E8F0DE186FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="4" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
   <sheets>
     <sheet name="veda input" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="248">
   <si>
     <t>ACT_MINLD</t>
   </si>
@@ -2596,21 +2596,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> can be challenging if oil seeped into ground over years. Oil can create a long-term pollution plume, so regulations require thorough cleanup (soil excavation or in-situ treatment) in many jurisdictions. This is labor- and cost-intensive and is often the largest single cost item, much like coal ash is for coal plants. Salvage helps (old oil tanks can be scrapped, equipment sold), but it may not offset the high cleanup costs. Uncertainty is high, hinging on how contaminated the site is. Some old oil plants that operated only sparingly may have minimal contamination and thus be relatively cheap to retire (~$30–40/kW), whereas others that ran for decades and leaked oil could be at the upper end or beyond.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Sources:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> All cost estimates are derived from industry reports and case studies. For example, Raimi (2017) provides average and range for U.S. plant decommissioning costs by fuel, which we have updated to 2023 USD. Additional data from World Bank/ESMAP, Gold Standard, NewClimate Institute, and World Nuclear Association/IAEA inform the figures. Where specific technologies have not yet been decommissioned (e.g. CCS-equipped plants, SMRs), we have indicated that no direct sources exist and provided reasoned estimates (with assumptions noted). All ranges reflect low/high scenarios; higher-end costs usually assume more extensive environmental remediation per regional regulatory requirements.</t>
     </r>
   </si>
   <si>
@@ -2948,6 +2933,81 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>545307</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>176211</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2976562</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>4763</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BDC4EF9-5E8A-2F58-6455-1CFB661B4753}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="545307" y="40285986"/>
+          <a:ext cx="8170068" cy="1276352"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>Sources: All cost estimates are derived from industry reports and case studies. For example, Raimi (2017) provides average and range for U.S. plant decommissioning costs by fuel, which we have updated to 2023 USD. Additional data from World Bank/ESMAP, Gold Standard, NewClimate Institute, and World Nuclear Association/IAEA inform the figures. Where specific technologies have not yet been decommissioned (e.g. CCS-equipped plants, SMRs), we have indicated that no direct sources exist and provided reasoned estimates (with assumptions noted). All ranges reflect low/high scenarios; higher-end costs usually assume more extensive environmental remediation per regional regulatory requirements.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3273,7 +3333,7 @@
   <sheetData>
     <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="D2" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>90</v>
@@ -3311,7 +3371,7 @@
         <v>82</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M3" s="9"/>
       <c r="N3" s="3" t="s">
@@ -4073,7 +4133,7 @@
         <v>0.1</v>
       </c>
       <c r="H17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>83</v>
@@ -4162,39 +4222,39 @@
   <sheetData>
     <row r="2" spans="2:50" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="AD2" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="3" spans="2:50" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" t="s">
         <v>203</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>204</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>205</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>206</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>207</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>208</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>209</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>210</v>
-      </c>
-      <c r="J3" t="s">
-        <v>211</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -4242,7 +4302,7 @@
         <v>200</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AE3" s="3">
         <f t="shared" ref="AE3:AS4" si="0">K3</f>
@@ -4307,25 +4367,25 @@
     </row>
     <row r="4" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4" t="s">
         <v>213</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>214</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F4" t="s">
         <v>215</v>
-      </c>
-      <c r="E4" t="s">
-        <v>215</v>
-      </c>
-      <c r="F4" t="s">
-        <v>216</v>
       </c>
       <c r="G4" s="17">
         <v>39.18</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I4" s="17">
         <v>43.5</v>
@@ -4445,25 +4505,25 @@
     </row>
     <row r="5" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" t="s">
         <v>218</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F5" t="s">
         <v>215</v>
-      </c>
-      <c r="D5" t="s">
-        <v>219</v>
-      </c>
-      <c r="E5" t="s">
-        <v>215</v>
-      </c>
-      <c r="F5" t="s">
-        <v>216</v>
       </c>
       <c r="G5" s="17">
         <v>19.34</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I5" s="17">
         <v>28.67</v>
@@ -4583,30 +4643,30 @@
     </row>
     <row r="7" spans="2:50" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AD7" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="2:50" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C8" t="s">
         <v>203</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>204</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>205</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>206</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>207</v>
       </c>
-      <c r="G8" t="s">
-        <v>208</v>
-      </c>
       <c r="H8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -4669,7 +4729,7 @@
         <v>200</v>
       </c>
       <c r="AD8" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AE8" s="3">
         <f t="shared" ref="AE8:AT10" si="2">I8</f>
@@ -4754,19 +4814,19 @@
     </row>
     <row r="9" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" t="s">
+        <v>214</v>
+      </c>
+      <c r="F9" t="s">
         <v>220</v>
-      </c>
-      <c r="C9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E9" t="s">
-        <v>215</v>
-      </c>
-      <c r="F9" t="s">
-        <v>221</v>
       </c>
       <c r="G9" s="17">
         <v>30.18</v>
@@ -4921,19 +4981,19 @@
     </row>
     <row r="10" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G10" s="17">
         <v>19.73</v>
@@ -5088,47 +5148,47 @@
     </row>
     <row r="13" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B13" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B14" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
     </row>
     <row r="15" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B15" s="18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
     </row>
     <row r="16" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B16" s="18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B18" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="D18" s="18" t="s">
         <v>228</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B19" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>230</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>231</v>
       </c>
       <c r="D19" s="18">
         <v>253</v>
@@ -5136,36 +5196,36 @@
     </row>
     <row r="20" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D20" s="18">
         <v>203</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B21" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C21" s="18" t="s">
         <v>234</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>235</v>
       </c>
       <c r="D21" s="18">
         <v>82</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="K21" s="3">
         <v>2019</v>
@@ -5176,22 +5236,22 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B22" s="18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D22" s="18">
         <v>242</v>
       </c>
       <c r="H22" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I22" t="s">
+        <v>245</v>
+      </c>
+      <c r="J22" t="s">
         <v>246</v>
-      </c>
-      <c r="J22" t="s">
-        <v>247</v>
       </c>
       <c r="K22">
         <f>AD4</f>
@@ -5203,16 +5263,16 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B23" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D23" s="18">
         <v>226</v>
       </c>
       <c r="H23" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I23" t="s">
         <v>80</v>
@@ -5227,16 +5287,16 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B24" s="18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D24" s="18">
         <v>174</v>
       </c>
       <c r="H24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
@@ -5251,16 +5311,16 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B25" s="18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D25" s="18">
         <v>258</v>
       </c>
       <c r="H25" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I25" t="s">
         <v>15</v>
@@ -5275,10 +5335,10 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B26" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="C26" s="18" t="s">
         <v>244</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>245</v>
       </c>
       <c r="D26" s="18">
         <v>135</v>
@@ -5967,7 +6027,7 @@
         <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
@@ -6501,12 +6561,11 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A25" s="15" t="s">
-        <v>197</v>
-      </c>
+      <c r="A25" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88199344-6D9C-45B5-B9E0-E8F0DE186FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E25BEB-3AD9-4047-893F-A421EDB16807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="4" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
   <sheets>
     <sheet name="veda input" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="dcost_data" sheetId="6" r:id="rId4"/>
     <sheet name="readme_dcost" sheetId="5" r:id="rId5"/>
     <sheet name="uc_tech_map" sheetId="4" r:id="rId6"/>
+    <sheet name="DEF topology" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_CH">110000</definedName>
@@ -67,8 +68,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={34ED3C89-69D4-4FF1-94CC-CE0D879943AA}</author>
+  </authors>
+  <commentList>
+    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{34ED3C89-69D4-4FF1-94CC-CE0D879943AA}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    CAP (nonRE) &gt; COMPRD (DEF_C) </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="279">
   <si>
     <t>ACT_MINLD</t>
   </si>
@@ -2750,6 +2769,99 @@
   </si>
   <si>
     <t>Nuclear P</t>
+  </si>
+  <si>
+    <t>~TFM_TOPINS</t>
+  </si>
+  <si>
+    <t>process</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>io</t>
+  </si>
+  <si>
+    <t>ELC4H,ELC8H,ELC</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>ELC4H,ELC</t>
+  </si>
+  <si>
+    <t>ELC4H,ELC8H</t>
+  </si>
+  <si>
+    <t>OUT</t>
+  </si>
+  <si>
+    <t>~UC_Sets: R_E: AllRegions</t>
+  </si>
+  <si>
+    <t>~UC_T: LO</t>
+  </si>
+  <si>
+    <t>UC_N</t>
+  </si>
+  <si>
+    <t>PSET_PN</t>
+  </si>
+  <si>
+    <t>Pset_CI</t>
+  </si>
+  <si>
+    <t>PSET_CO</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>UC_CAP</t>
+  </si>
+  <si>
+    <t>UC_COMPRD</t>
+  </si>
+  <si>
+    <t>UC_RHSRT</t>
+  </si>
+  <si>
+    <t>UC_RHSRT~0</t>
+  </si>
+  <si>
+    <t>UC_Desc</t>
+  </si>
+  <si>
+    <t>UCE_Min-DispatchableCAP</t>
+  </si>
+  <si>
+    <t>ELE,CHP</t>
+  </si>
+  <si>
+    <t>E*</t>
+  </si>
+  <si>
+    <t>Min dispatchable capacity for VRE portfolio</t>
+  </si>
+  <si>
+    <t>DEF_C</t>
+  </si>
+  <si>
+    <t>*stg8hb*</t>
+  </si>
+  <si>
+    <t>*stg4hb*</t>
+  </si>
+  <si>
+    <t>distr*</t>
+  </si>
+  <si>
+    <t>*,-solar,-wind*,-ELC,-ELCSPV,-elc[_]???[_]*</t>
   </si>
 </sst>
 </file>
@@ -2829,7 +2941,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2839,6 +2951,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2875,7 +2993,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
@@ -2915,6 +3033,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Good" xfId="3" builtinId="26"/>
@@ -3008,6 +3127,12 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="黄 凱凱(Kaikai Huang)" id="{9D5651AD-03AB-49CF-BE42-59AD7CA83975}" userId="S::J2412140@jera.co.jp::f9b6adb6-b751-4da6-9b6e-314b902b48bf" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3305,6 +3430,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="H20" dT="2026-04-17T06:07:36.14" personId="{9D5651AD-03AB-49CF-BE42-59AD7CA83975}" id="{34ED3C89-69D4-4FF1-94CC-CE0D879943AA}">
+    <text xml:space="preserve">CAP (nonRE) &gt; COMPRD (DEF_C) </text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75F77616-F3F2-4CAD-9718-D78F2778A52A}">
   <dimension ref="B2:S17"/>
@@ -6644,4 +6777,151 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F268AA5-7930-4A9B-8922-4C67ECE05AA1}">
+  <dimension ref="B3:M23"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B3" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="H20" s="19" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>259</v>
+      </c>
+      <c r="C21" t="s">
+        <v>236</v>
+      </c>
+      <c r="D21" t="s">
+        <v>260</v>
+      </c>
+      <c r="E21" t="s">
+        <v>261</v>
+      </c>
+      <c r="F21" t="s">
+        <v>262</v>
+      </c>
+      <c r="G21" t="s">
+        <v>263</v>
+      </c>
+      <c r="H21" t="s">
+        <v>264</v>
+      </c>
+      <c r="I21" t="s">
+        <v>265</v>
+      </c>
+      <c r="J21" t="s">
+        <v>266</v>
+      </c>
+      <c r="K21" t="s">
+        <v>267</v>
+      </c>
+      <c r="L21" t="s">
+        <v>268</v>
+      </c>
+      <c r="M21" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>270</v>
+      </c>
+      <c r="C22" t="s">
+        <v>271</v>
+      </c>
+      <c r="D22" t="s">
+        <v>272</v>
+      </c>
+      <c r="E22" t="s">
+        <v>278</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>5</v>
+      </c>
+      <c r="M22" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="G23" t="s">
+        <v>274</v>
+      </c>
+      <c r="J23">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E25BEB-3AD9-4047-893F-A421EDB16807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C6DB7F-B752-42A9-AFCB-B93B348F73E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="278">
   <si>
     <t>ACT_MINLD</t>
   </si>
@@ -2843,9 +2843,6 @@
     <t>ELE,CHP</t>
   </si>
   <si>
-    <t>E*</t>
-  </si>
-  <si>
     <t>Min dispatchable capacity for VRE portfolio</t>
   </si>
   <si>
@@ -2861,7 +2858,7 @@
     <t>distr*</t>
   </si>
   <si>
-    <t>*,-solar,-wind*,-ELC,-ELCSPV,-elc[_]???[_]*</t>
+    <t>*,-solar,-wind*,-ELC,-ELCSPV,-elc[_]???[_]*,-e[_]*</t>
   </si>
 </sst>
 </file>
@@ -6807,7 +6804,7 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C5" t="s">
         <v>252</v>
@@ -6818,7 +6815,7 @@
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C6" t="s">
         <v>254</v>
@@ -6829,7 +6826,7 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C7" t="s">
         <v>255</v>
@@ -6893,11 +6890,8 @@
       <c r="C22" t="s">
         <v>271</v>
       </c>
-      <c r="D22" t="s">
-        <v>272</v>
-      </c>
       <c r="E22" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -6909,12 +6903,12 @@
         <v>5</v>
       </c>
       <c r="M22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.45">
       <c r="G23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J23">
         <v>-1</v>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C6DB7F-B752-42A9-AFCB-B93B348F73E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88199344-6D9C-45B5-B9E0-E8F0DE186FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="4" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
   <sheets>
     <sheet name="veda input" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="dcost_data" sheetId="6" r:id="rId4"/>
     <sheet name="readme_dcost" sheetId="5" r:id="rId5"/>
     <sheet name="uc_tech_map" sheetId="4" r:id="rId6"/>
-    <sheet name="DEF topology" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_CH">110000</definedName>
@@ -68,26 +67,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={34ED3C89-69D4-4FF1-94CC-CE0D879943AA}</author>
-  </authors>
-  <commentList>
-    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{34ED3C89-69D4-4FF1-94CC-CE0D879943AA}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    CAP (nonRE) &gt; COMPRD (DEF_C) </t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="248">
   <si>
     <t>ACT_MINLD</t>
   </si>
@@ -2769,96 +2750,6 @@
   </si>
   <si>
     <t>Nuclear P</t>
-  </si>
-  <si>
-    <t>~TFM_TOPINS</t>
-  </si>
-  <si>
-    <t>process</t>
-  </si>
-  <si>
-    <t>commodity</t>
-  </si>
-  <si>
-    <t>io</t>
-  </si>
-  <si>
-    <t>ELC4H,ELC8H,ELC</t>
-  </si>
-  <si>
-    <t>IN</t>
-  </si>
-  <si>
-    <t>ELC4H,ELC</t>
-  </si>
-  <si>
-    <t>ELC4H,ELC8H</t>
-  </si>
-  <si>
-    <t>OUT</t>
-  </si>
-  <si>
-    <t>~UC_Sets: R_E: AllRegions</t>
-  </si>
-  <si>
-    <t>~UC_T: LO</t>
-  </si>
-  <si>
-    <t>UC_N</t>
-  </si>
-  <si>
-    <t>PSET_PN</t>
-  </si>
-  <si>
-    <t>Pset_CI</t>
-  </si>
-  <si>
-    <t>PSET_CO</t>
-  </si>
-  <si>
-    <t>Cset_CN</t>
-  </si>
-  <si>
-    <t>TimeSlice</t>
-  </si>
-  <si>
-    <t>UC_CAP</t>
-  </si>
-  <si>
-    <t>UC_COMPRD</t>
-  </si>
-  <si>
-    <t>UC_RHSRT</t>
-  </si>
-  <si>
-    <t>UC_RHSRT~0</t>
-  </si>
-  <si>
-    <t>UC_Desc</t>
-  </si>
-  <si>
-    <t>UCE_Min-DispatchableCAP</t>
-  </si>
-  <si>
-    <t>ELE,CHP</t>
-  </si>
-  <si>
-    <t>Min dispatchable capacity for VRE portfolio</t>
-  </si>
-  <si>
-    <t>DEF_C</t>
-  </si>
-  <si>
-    <t>*stg8hb*</t>
-  </si>
-  <si>
-    <t>*stg4hb*</t>
-  </si>
-  <si>
-    <t>distr*</t>
-  </si>
-  <si>
-    <t>*,-solar,-wind*,-ELC,-ELCSPV,-elc[_]???[_]*,-e[_]*</t>
   </si>
 </sst>
 </file>
@@ -2938,7 +2829,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2948,12 +2839,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2990,7 +2875,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
@@ -3030,7 +2915,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Good" xfId="3" builtinId="26"/>
@@ -3124,12 +3008,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="黄 凱凱(Kaikai Huang)" id="{9D5651AD-03AB-49CF-BE42-59AD7CA83975}" userId="S::J2412140@jera.co.jp::f9b6adb6-b751-4da6-9b6e-314b902b48bf" providerId="AD"/>
-</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3427,14 +3305,6 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="H20" dT="2026-04-17T06:07:36.14" personId="{9D5651AD-03AB-49CF-BE42-59AD7CA83975}" id="{34ED3C89-69D4-4FF1-94CC-CE0D879943AA}">
-    <text xml:space="preserve">CAP (nonRE) &gt; COMPRD (DEF_C) </text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75F77616-F3F2-4CAD-9718-D78F2778A52A}">
   <dimension ref="B2:S17"/>
@@ -6774,148 +6644,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F268AA5-7930-4A9B-8922-4C67ECE05AA1}">
-  <dimension ref="B3:M23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B3" s="19" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B4" t="s">
-        <v>249</v>
-      </c>
-      <c r="C4" t="s">
-        <v>250</v>
-      </c>
-      <c r="D4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C5" t="s">
-        <v>252</v>
-      </c>
-      <c r="D5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B6" t="s">
-        <v>275</v>
-      </c>
-      <c r="C6" t="s">
-        <v>254</v>
-      </c>
-      <c r="D6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C7" t="s">
-        <v>255</v>
-      </c>
-      <c r="D7" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B17" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="H20" s="19" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B21" t="s">
-        <v>259</v>
-      </c>
-      <c r="C21" t="s">
-        <v>236</v>
-      </c>
-      <c r="D21" t="s">
-        <v>260</v>
-      </c>
-      <c r="E21" t="s">
-        <v>261</v>
-      </c>
-      <c r="F21" t="s">
-        <v>262</v>
-      </c>
-      <c r="G21" t="s">
-        <v>263</v>
-      </c>
-      <c r="H21" t="s">
-        <v>264</v>
-      </c>
-      <c r="I21" t="s">
-        <v>265</v>
-      </c>
-      <c r="J21" t="s">
-        <v>266</v>
-      </c>
-      <c r="K21" t="s">
-        <v>267</v>
-      </c>
-      <c r="L21" t="s">
-        <v>268</v>
-      </c>
-      <c r="M21" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B22" t="s">
-        <v>270</v>
-      </c>
-      <c r="C22" t="s">
-        <v>271</v>
-      </c>
-      <c r="E22" t="s">
-        <v>277</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>5</v>
-      </c>
-      <c r="M22" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="G23" t="s">
-        <v>273</v>
-      </c>
-      <c r="J23">
-        <v>-1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88199344-6D9C-45B5-B9E0-E8F0DE186FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C6DB7F-B752-42A9-AFCB-B93B348F73E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="4" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
   <sheets>
     <sheet name="veda input" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="dcost_data" sheetId="6" r:id="rId4"/>
     <sheet name="readme_dcost" sheetId="5" r:id="rId5"/>
     <sheet name="uc_tech_map" sheetId="4" r:id="rId6"/>
+    <sheet name="DEF topology" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_CH">110000</definedName>
@@ -67,8 +68,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={34ED3C89-69D4-4FF1-94CC-CE0D879943AA}</author>
+  </authors>
+  <commentList>
+    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{34ED3C89-69D4-4FF1-94CC-CE0D879943AA}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    CAP (nonRE) &gt; COMPRD (DEF_C) </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="278">
   <si>
     <t>ACT_MINLD</t>
   </si>
@@ -2750,6 +2769,96 @@
   </si>
   <si>
     <t>Nuclear P</t>
+  </si>
+  <si>
+    <t>~TFM_TOPINS</t>
+  </si>
+  <si>
+    <t>process</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>io</t>
+  </si>
+  <si>
+    <t>ELC4H,ELC8H,ELC</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>ELC4H,ELC</t>
+  </si>
+  <si>
+    <t>ELC4H,ELC8H</t>
+  </si>
+  <si>
+    <t>OUT</t>
+  </si>
+  <si>
+    <t>~UC_Sets: R_E: AllRegions</t>
+  </si>
+  <si>
+    <t>~UC_T: LO</t>
+  </si>
+  <si>
+    <t>UC_N</t>
+  </si>
+  <si>
+    <t>PSET_PN</t>
+  </si>
+  <si>
+    <t>Pset_CI</t>
+  </si>
+  <si>
+    <t>PSET_CO</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>UC_CAP</t>
+  </si>
+  <si>
+    <t>UC_COMPRD</t>
+  </si>
+  <si>
+    <t>UC_RHSRT</t>
+  </si>
+  <si>
+    <t>UC_RHSRT~0</t>
+  </si>
+  <si>
+    <t>UC_Desc</t>
+  </si>
+  <si>
+    <t>UCE_Min-DispatchableCAP</t>
+  </si>
+  <si>
+    <t>ELE,CHP</t>
+  </si>
+  <si>
+    <t>Min dispatchable capacity for VRE portfolio</t>
+  </si>
+  <si>
+    <t>DEF_C</t>
+  </si>
+  <si>
+    <t>*stg8hb*</t>
+  </si>
+  <si>
+    <t>*stg4hb*</t>
+  </si>
+  <si>
+    <t>distr*</t>
+  </si>
+  <si>
+    <t>*,-solar,-wind*,-ELC,-ELCSPV,-elc[_]???[_]*,-e[_]*</t>
   </si>
 </sst>
 </file>
@@ -2829,7 +2938,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2839,6 +2948,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2875,7 +2990,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
@@ -2915,6 +3030,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Good" xfId="3" builtinId="26"/>
@@ -3008,6 +3124,12 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="黄 凱凱(Kaikai Huang)" id="{9D5651AD-03AB-49CF-BE42-59AD7CA83975}" userId="S::J2412140@jera.co.jp::f9b6adb6-b751-4da6-9b6e-314b902b48bf" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3305,6 +3427,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="H20" dT="2026-04-17T06:07:36.14" personId="{9D5651AD-03AB-49CF-BE42-59AD7CA83975}" id="{34ED3C89-69D4-4FF1-94CC-CE0D879943AA}">
+    <text xml:space="preserve">CAP (nonRE) &gt; COMPRD (DEF_C) </text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75F77616-F3F2-4CAD-9718-D78F2778A52A}">
   <dimension ref="B2:S17"/>
@@ -6644,4 +6774,148 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F268AA5-7930-4A9B-8922-4C67ECE05AA1}">
+  <dimension ref="B3:M23"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B3" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="H20" s="19" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>259</v>
+      </c>
+      <c r="C21" t="s">
+        <v>236</v>
+      </c>
+      <c r="D21" t="s">
+        <v>260</v>
+      </c>
+      <c r="E21" t="s">
+        <v>261</v>
+      </c>
+      <c r="F21" t="s">
+        <v>262</v>
+      </c>
+      <c r="G21" t="s">
+        <v>263</v>
+      </c>
+      <c r="H21" t="s">
+        <v>264</v>
+      </c>
+      <c r="I21" t="s">
+        <v>265</v>
+      </c>
+      <c r="J21" t="s">
+        <v>266</v>
+      </c>
+      <c r="K21" t="s">
+        <v>267</v>
+      </c>
+      <c r="L21" t="s">
+        <v>268</v>
+      </c>
+      <c r="M21" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>270</v>
+      </c>
+      <c r="C22" t="s">
+        <v>271</v>
+      </c>
+      <c r="E22" t="s">
+        <v>277</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>5</v>
+      </c>
+      <c r="M22" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="G23" t="s">
+        <v>273</v>
+      </c>
+      <c r="J23">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88199344-6D9C-45B5-B9E0-E8F0DE186FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A40FA9-B09D-45E4-B1A4-6DC9156DC1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="4" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
   <sheets>
     <sheet name="veda input" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="dcost_data" sheetId="6" r:id="rId4"/>
     <sheet name="readme_dcost" sheetId="5" r:id="rId5"/>
     <sheet name="uc_tech_map" sheetId="4" r:id="rId6"/>
+    <sheet name="DEF topology" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_CH">110000</definedName>
@@ -67,8 +68,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={A48137D9-1046-4493-80F0-367656025934}</author>
+  </authors>
+  <commentList>
+    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{A48137D9-1046-4493-80F0-367656025934}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    CAP (nonRE) &gt; COMPRD (DEF_C) </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="278">
   <si>
     <t>ACT_MINLD</t>
   </si>
@@ -2750,13 +2769,103 @@
   </si>
   <si>
     <t>Nuclear P</t>
+  </si>
+  <si>
+    <t>~TFM_TOPINS</t>
+  </si>
+  <si>
+    <t>process</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>io</t>
+  </si>
+  <si>
+    <t>*stg8hb*</t>
+  </si>
+  <si>
+    <t>ELC4H,ELC8H,ELC</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>*stg4hb*</t>
+  </si>
+  <si>
+    <t>ELC4H,ELC</t>
+  </si>
+  <si>
+    <t>distr*</t>
+  </si>
+  <si>
+    <t>ELC4H,ELC8H</t>
+  </si>
+  <si>
+    <t>OUT</t>
+  </si>
+  <si>
+    <t>~UC_Sets: R_E: AllRegions</t>
+  </si>
+  <si>
+    <t>~UC_T: LO</t>
+  </si>
+  <si>
+    <t>UC_N</t>
+  </si>
+  <si>
+    <t>PSET_PN</t>
+  </si>
+  <si>
+    <t>Pset_CI</t>
+  </si>
+  <si>
+    <t>PSET_CO</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>UC_CAP</t>
+  </si>
+  <si>
+    <t>UC_COMPRD</t>
+  </si>
+  <si>
+    <t>UC_RHSRT</t>
+  </si>
+  <si>
+    <t>UC_RHSRT~0</t>
+  </si>
+  <si>
+    <t>UC_Desc</t>
+  </si>
+  <si>
+    <t>UCE_Min-DispatchableCAP</t>
+  </si>
+  <si>
+    <t>ELE,CHP</t>
+  </si>
+  <si>
+    <t>*,-solar,-wind*,-ELC,-ELCSPV,-elc[_]???[_]*,-e[_]*</t>
+  </si>
+  <si>
+    <t>Min dispatchable capacity for VRE portfolio</t>
+  </si>
+  <si>
+    <t>DEF_C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2828,8 +2937,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2839,6 +2954,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2875,7 +2996,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
@@ -2915,6 +3036,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Good" xfId="3" builtinId="26"/>
@@ -3008,6 +3130,12 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="黄 凱凱(Kaikai Huang)" id="{FB46E857-4E02-49E8-BDCC-693D94FA396C}" userId="S::J2412140@jera.co.jp::f9b6adb6-b751-4da6-9b6e-314b902b48bf" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3305,6 +3433,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="H20" dT="2026-04-17T06:07:36.14" personId="{FB46E857-4E02-49E8-BDCC-693D94FA396C}" id="{A48137D9-1046-4493-80F0-367656025934}">
+    <text xml:space="preserve">CAP (nonRE) &gt; COMPRD (DEF_C) </text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75F77616-F3F2-4CAD-9718-D78F2778A52A}">
   <dimension ref="B2:S17"/>
@@ -6644,4 +6780,148 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22251C8D-B089-455B-A382-CAE474AB152B}">
+  <dimension ref="B3:M23"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B3" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" t="s">
+        <v>256</v>
+      </c>
+      <c r="D6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>257</v>
+      </c>
+      <c r="C7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="H20" s="19" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>262</v>
+      </c>
+      <c r="C21" t="s">
+        <v>236</v>
+      </c>
+      <c r="D21" t="s">
+        <v>263</v>
+      </c>
+      <c r="E21" t="s">
+        <v>264</v>
+      </c>
+      <c r="F21" t="s">
+        <v>265</v>
+      </c>
+      <c r="G21" t="s">
+        <v>266</v>
+      </c>
+      <c r="H21" t="s">
+        <v>267</v>
+      </c>
+      <c r="I21" t="s">
+        <v>268</v>
+      </c>
+      <c r="J21" t="s">
+        <v>269</v>
+      </c>
+      <c r="K21" t="s">
+        <v>270</v>
+      </c>
+      <c r="L21" t="s">
+        <v>271</v>
+      </c>
+      <c r="M21" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>273</v>
+      </c>
+      <c r="C22" t="s">
+        <v>274</v>
+      </c>
+      <c r="E22" t="s">
+        <v>275</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>5</v>
+      </c>
+      <c r="M22" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="G23" t="s">
+        <v>277</v>
+      </c>
+      <c r="J23">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A40FA9-B09D-45E4-B1A4-6DC9156DC1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4AEE76-C40B-424C-93BC-4F006654EBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
@@ -71,10 +71,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={A48137D9-1046-4493-80F0-367656025934}</author>
+    <author>tc={34ED3C89-69D4-4FF1-94CC-CE0D879943AA}</author>
   </authors>
   <commentList>
-    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{A48137D9-1046-4493-80F0-367656025934}">
+    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{34ED3C89-69D4-4FF1-94CC-CE0D879943AA}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="277">
   <si>
     <t>ACT_MINLD</t>
   </si>
@@ -2783,89 +2783,86 @@
     <t>io</t>
   </si>
   <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>ELC4H,ELC8H</t>
+  </si>
+  <si>
+    <t>OUT</t>
+  </si>
+  <si>
+    <t>~UC_Sets: R_E: AllRegions</t>
+  </si>
+  <si>
+    <t>~UC_T: LO</t>
+  </si>
+  <si>
+    <t>UC_N</t>
+  </si>
+  <si>
+    <t>PSET_PN</t>
+  </si>
+  <si>
+    <t>Pset_CI</t>
+  </si>
+  <si>
+    <t>PSET_CO</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>UC_CAP</t>
+  </si>
+  <si>
+    <t>UC_COMPRD</t>
+  </si>
+  <si>
+    <t>UC_RHSRT</t>
+  </si>
+  <si>
+    <t>UC_RHSRT~0</t>
+  </si>
+  <si>
+    <t>UC_Desc</t>
+  </si>
+  <si>
+    <t>UCE_Min-DispatchableCAP</t>
+  </si>
+  <si>
+    <t>ELE,CHP</t>
+  </si>
+  <si>
+    <t>Min dispatchable capacity for VRE portfolio</t>
+  </si>
+  <si>
+    <t>DEF_C</t>
+  </si>
+  <si>
     <t>*stg8hb*</t>
   </si>
   <si>
-    <t>ELC4H,ELC8H,ELC</t>
-  </si>
-  <si>
-    <t>IN</t>
-  </si>
-  <si>
     <t>*stg4hb*</t>
   </si>
   <si>
-    <t>ELC4H,ELC</t>
-  </si>
-  <si>
     <t>distr*</t>
   </si>
   <si>
-    <t>ELC4H,ELC8H</t>
-  </si>
-  <si>
-    <t>OUT</t>
-  </si>
-  <si>
-    <t>~UC_Sets: R_E: AllRegions</t>
-  </si>
-  <si>
-    <t>~UC_T: LO</t>
-  </si>
-  <si>
-    <t>UC_N</t>
-  </si>
-  <si>
-    <t>PSET_PN</t>
-  </si>
-  <si>
-    <t>Pset_CI</t>
-  </si>
-  <si>
-    <t>PSET_CO</t>
-  </si>
-  <si>
-    <t>Cset_CN</t>
-  </si>
-  <si>
-    <t>TimeSlice</t>
-  </si>
-  <si>
-    <t>UC_CAP</t>
-  </si>
-  <si>
-    <t>UC_COMPRD</t>
-  </si>
-  <si>
-    <t>UC_RHSRT</t>
-  </si>
-  <si>
-    <t>UC_RHSRT~0</t>
-  </si>
-  <si>
-    <t>UC_Desc</t>
-  </si>
-  <si>
-    <t>UCE_Min-DispatchableCAP</t>
-  </si>
-  <si>
-    <t>ELE,CHP</t>
-  </si>
-  <si>
     <t>*,-solar,-wind*,-ELC,-ELCSPV,-elc[_]???[_]*,-e[_]*</t>
   </si>
   <si>
-    <t>Min dispatchable capacity for VRE portfolio</t>
-  </si>
-  <si>
-    <t>DEF_C</t>
+    <t>ELC4H</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2936,12 +2933,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -3134,7 +3125,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="黄 凱凱(Kaikai Huang)" id="{FB46E857-4E02-49E8-BDCC-693D94FA396C}" userId="S::J2412140@jera.co.jp::f9b6adb6-b751-4da6-9b6e-314b902b48bf" providerId="AD"/>
+  <person displayName="黄 凱凱(Kaikai Huang)" id="{9D5651AD-03AB-49CF-BE42-59AD7CA83975}" userId="S::J2412140@jera.co.jp::f9b6adb6-b751-4da6-9b6e-314b902b48bf" providerId="AD"/>
 </personList>
 </file>
 
@@ -3435,7 +3426,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="H20" dT="2026-04-17T06:07:36.14" personId="{FB46E857-4E02-49E8-BDCC-693D94FA396C}" id="{A48137D9-1046-4493-80F0-367656025934}">
+  <threadedComment ref="H20" dT="2026-04-17T06:07:36.14" personId="{9D5651AD-03AB-49CF-BE42-59AD7CA83975}" id="{34ED3C89-69D4-4FF1-94CC-CE0D879943AA}">
     <text xml:space="preserve">CAP (nonRE) &gt; COMPRD (DEF_C) </text>
   </threadedComment>
 </ThreadedComments>
@@ -6783,7 +6774,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22251C8D-B089-455B-A382-CAE474AB152B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F268AA5-7930-4A9B-8922-4C67ECE05AA1}">
   <dimension ref="B3:M23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -6810,91 +6801,91 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C5" t="s">
         <v>253</v>
       </c>
       <c r="D5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="C6" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="D6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="C7" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D7" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.45">
       <c r="H20" s="19" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C21" t="s">
         <v>236</v>
       </c>
       <c r="D21" t="s">
+        <v>258</v>
+      </c>
+      <c r="E21" t="s">
+        <v>259</v>
+      </c>
+      <c r="F21" t="s">
+        <v>260</v>
+      </c>
+      <c r="G21" t="s">
+        <v>261</v>
+      </c>
+      <c r="H21" t="s">
+        <v>262</v>
+      </c>
+      <c r="I21" t="s">
         <v>263</v>
       </c>
-      <c r="E21" t="s">
+      <c r="J21" t="s">
         <v>264</v>
       </c>
-      <c r="F21" t="s">
+      <c r="K21" t="s">
         <v>265</v>
       </c>
-      <c r="G21" t="s">
+      <c r="L21" t="s">
         <v>266</v>
       </c>
-      <c r="H21" t="s">
+      <c r="M21" t="s">
         <v>267</v>
-      </c>
-      <c r="I21" t="s">
-        <v>268</v>
-      </c>
-      <c r="J21" t="s">
-        <v>269</v>
-      </c>
-      <c r="K21" t="s">
-        <v>270</v>
-      </c>
-      <c r="L21" t="s">
-        <v>271</v>
-      </c>
-      <c r="M21" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C22" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="E22" t="s">
         <v>275</v>
@@ -6909,12 +6900,12 @@
         <v>5</v>
       </c>
       <c r="M22" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.45">
       <c r="G23" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="J23">
         <v>-1</v>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4AEE76-C40B-424C-93BC-4F006654EBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDABE634-E17C-4042-848B-90D51F772654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
   <sheets>
     <sheet name="veda input" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="278">
   <si>
     <t>ACT_MINLD</t>
   </si>
@@ -2856,6 +2856,9 @@
   </si>
   <si>
     <t>ELC4H</t>
+  </si>
+  <si>
+    <t>Gas Turbine*</t>
   </si>
 </sst>
 </file>
@@ -2987,7 +2990,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
@@ -3028,6 +3031,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Good" xfId="3" builtinId="26"/>
@@ -3434,7 +3438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75F77616-F3F2-4CAD-9718-D78F2778A52A}">
-  <dimension ref="B2:S17"/>
+  <dimension ref="B2:S18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.73046875" bestFit="1" customWidth="1"/>
@@ -4292,11 +4296,62 @@
         <v>-aggregated*</v>
       </c>
     </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B18" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="F18" s="15">
+        <v>1.2</v>
+      </c>
+      <c r="G18" s="15">
+        <v>0.01</v>
+      </c>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="L18" s="20">
+        <f>L6</f>
+        <v>30</v>
+      </c>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="O18" s="15">
+        <v>1.2</v>
+      </c>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15" t="str">
+        <f t="shared" ref="Q18" si="4">IF(I18="","",I18)</f>
+        <v/>
+      </c>
+      <c r="R18" s="15" t="str">
+        <f t="shared" ref="R18" si="5">IF(J18="","",J18)</f>
+        <v/>
+      </c>
+      <c r="S18" s="15" t="str">
+        <f t="shared" ref="S18" si="6">IF(K18="","",K18)</f>
+        <v>Gas Turbine*</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:P17">
     <sortCondition ref="A4:A17"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDABE634-E17C-4042-848B-90D51F772654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB90C42-B5A5-4CA1-9F30-F34DDE91013A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
@@ -454,9 +454,6 @@
     <t>Subcritical Coal, bioenergy</t>
   </si>
   <si>
-    <t>Supercritical Coal, IGCC</t>
-  </si>
-  <si>
     <t>~TFM_INS-AT: limtype=LO</t>
   </si>
   <si>
@@ -2859,6 +2856,9 @@
   </si>
   <si>
     <t>Gas Turbine*</t>
+  </si>
+  <si>
+    <t>Supercritical Coal, IGCC, coal_ccs</t>
   </si>
 </sst>
 </file>
@@ -3448,7 +3448,7 @@
     <col min="5" max="5" width="8.86328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.59765625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.1328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.1328125" bestFit="1" customWidth="1"/>
@@ -3456,7 +3456,7 @@
     <col min="13" max="13" width="8" customWidth="1"/>
     <col min="14" max="14" width="8.86328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.59765625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.1328125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7.33203125" bestFit="1" customWidth="1"/>
@@ -3464,10 +3464,10 @@
   <sheetData>
     <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="D2" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="2:19" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -3502,7 +3502,7 @@
         <v>82</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M3" s="9"/>
       <c r="N3" s="3" t="s">
@@ -4153,7 +4153,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="H15" t="s">
-        <v>89</v>
+        <v>277</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>83</v>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="P15" t="str">
         <f t="shared" si="0"/>
-        <v>Supercritical Coal, IGCC</v>
+        <v>Supercritical Coal, IGCC, coal_ccs</v>
       </c>
       <c r="Q15" t="str">
         <f t="shared" si="3"/>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="H16" t="str">
         <f>H15</f>
-        <v>Supercritical Coal, IGCC</v>
+        <v>Supercritical Coal, IGCC, coal_ccs</v>
       </c>
       <c r="I16" t="s">
         <v>76</v>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="P16" t="str">
         <f t="shared" si="0"/>
-        <v>Supercritical Coal, IGCC</v>
+        <v>Supercritical Coal, IGCC, coal_ccs</v>
       </c>
       <c r="Q16" t="str">
         <f t="shared" si="3"/>
@@ -4264,7 +4264,7 @@
         <v>0.1</v>
       </c>
       <c r="H17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>83</v>
@@ -4319,7 +4319,7 @@
       <c r="I18" s="15"/>
       <c r="J18" s="15"/>
       <c r="K18" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L18" s="20">
         <f>L6</f>
@@ -4404,39 +4404,39 @@
   <sheetData>
     <row r="2" spans="2:50" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="AD2" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="3" spans="2:50" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" t="s">
         <v>202</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>203</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>204</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>205</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>206</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>207</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>208</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>209</v>
-      </c>
-      <c r="J3" t="s">
-        <v>210</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -4484,7 +4484,7 @@
         <v>200</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AE3" s="3">
         <f t="shared" ref="AE3:AS4" si="0">K3</f>
@@ -4549,25 +4549,25 @@
     </row>
     <row r="4" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" t="s">
         <v>212</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>213</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" t="s">
         <v>214</v>
-      </c>
-      <c r="E4" t="s">
-        <v>214</v>
-      </c>
-      <c r="F4" t="s">
-        <v>215</v>
       </c>
       <c r="G4" s="17">
         <v>39.18</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I4" s="17">
         <v>43.5</v>
@@ -4687,25 +4687,25 @@
     </row>
     <row r="5" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D5" t="s">
         <v>217</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" t="s">
         <v>214</v>
-      </c>
-      <c r="D5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E5" t="s">
-        <v>214</v>
-      </c>
-      <c r="F5" t="s">
-        <v>215</v>
       </c>
       <c r="G5" s="17">
         <v>19.34</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I5" s="17">
         <v>28.67</v>
@@ -4825,30 +4825,30 @@
     </row>
     <row r="7" spans="2:50" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AD7" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="2:50" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8" t="s">
         <v>202</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>203</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>204</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>205</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>206</v>
       </c>
-      <c r="G8" t="s">
-        <v>207</v>
-      </c>
       <c r="H8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -4911,7 +4911,7 @@
         <v>200</v>
       </c>
       <c r="AD8" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AE8" s="3">
         <f t="shared" ref="AE8:AT10" si="2">I8</f>
@@ -4996,19 +4996,19 @@
     </row>
     <row r="9" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D9" t="s">
+        <v>213</v>
+      </c>
+      <c r="E9" t="s">
+        <v>213</v>
+      </c>
+      <c r="F9" t="s">
         <v>219</v>
-      </c>
-      <c r="C9" t="s">
-        <v>214</v>
-      </c>
-      <c r="D9" t="s">
-        <v>214</v>
-      </c>
-      <c r="E9" t="s">
-        <v>214</v>
-      </c>
-      <c r="F9" t="s">
-        <v>220</v>
       </c>
       <c r="G9" s="17">
         <v>30.18</v>
@@ -5163,19 +5163,19 @@
     </row>
     <row r="10" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G10" s="17">
         <v>19.73</v>
@@ -5330,47 +5330,47 @@
     </row>
     <row r="13" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B13" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B14" s="18" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
     </row>
     <row r="15" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B15" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
     </row>
     <row r="16" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B16" s="18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B18" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="D18" s="18" t="s">
         <v>227</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B19" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>229</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>230</v>
       </c>
       <c r="D19" s="18">
         <v>253</v>
@@ -5378,36 +5378,36 @@
     </row>
     <row r="20" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D20" s="18">
         <v>203</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B21" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="C21" s="18" t="s">
         <v>233</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>234</v>
       </c>
       <c r="D21" s="18">
         <v>82</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="K21" s="3">
         <v>2019</v>
@@ -5418,22 +5418,22 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B22" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D22" s="18">
         <v>242</v>
       </c>
       <c r="H22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I22" t="s">
+        <v>244</v>
+      </c>
+      <c r="J22" t="s">
         <v>245</v>
-      </c>
-      <c r="J22" t="s">
-        <v>246</v>
       </c>
       <c r="K22">
         <f>AD4</f>
@@ -5445,16 +5445,16 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B23" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D23" s="18">
         <v>226</v>
       </c>
       <c r="H23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I23" t="s">
         <v>80</v>
@@ -5469,16 +5469,16 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B24" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D24" s="18">
         <v>174</v>
       </c>
       <c r="H24" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
@@ -5493,16 +5493,16 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B25" s="18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D25" s="18">
         <v>258</v>
       </c>
       <c r="H25" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I25" t="s">
         <v>15</v>
@@ -5517,10 +5517,10 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B26" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="C26" s="18" t="s">
         <v>243</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>244</v>
       </c>
       <c r="D26" s="18">
         <v>135</v>
@@ -6209,7 +6209,7 @@
         <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
@@ -6382,364 +6382,364 @@
   <sheetData>
     <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="C3" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="D3" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="E3" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A4" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="D4" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="E4" s="14" t="s">
         <v>100</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="142.5" x14ac:dyDescent="0.45">
       <c r="A5" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="E5" s="14" t="s">
         <v>105</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="114" x14ac:dyDescent="0.45">
       <c r="A6" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="D6" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="E6" s="14" t="s">
         <v>110</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="185.25" x14ac:dyDescent="0.45">
       <c r="A7" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="C7" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="D7" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="E7" s="14" t="s">
         <v>115</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="128.25" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="C8" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="D8" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="E8" s="14" t="s">
         <v>120</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="128.25" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="C9" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="E9" s="14" t="s">
         <v>125</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="114" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="C10" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="D10" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="E10" s="14" t="s">
         <v>130</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="128.25" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="C11" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="D11" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="E11" s="14" t="s">
         <v>135</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="128.25" x14ac:dyDescent="0.45">
       <c r="A12" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="D12" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="E12" s="14" t="s">
         <v>140</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="185.25" x14ac:dyDescent="0.45">
       <c r="A13" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="D13" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="E13" s="14" t="s">
         <v>145</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="228" x14ac:dyDescent="0.45">
       <c r="A14" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="C14" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="D14" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="E14" s="14" t="s">
         <v>150</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="171" x14ac:dyDescent="0.45">
       <c r="A15" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="C15" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="D15" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="E15" s="14" t="s">
         <v>155</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="156.75" x14ac:dyDescent="0.45">
       <c r="A16" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="C16" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="D16" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="E16" s="14" t="s">
         <v>160</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="156.75" x14ac:dyDescent="0.45">
       <c r="A17" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="C17" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="D17" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="E17" s="14" t="s">
         <v>165</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="171" x14ac:dyDescent="0.45">
       <c r="A18" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="C18" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="D18" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="E18" s="14" t="s">
         <v>170</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="128.25" x14ac:dyDescent="0.45">
       <c r="A19" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="C19" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="D19" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="E19" s="14" t="s">
         <v>175</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="142.5" x14ac:dyDescent="0.45">
       <c r="A20" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="C20" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="D20" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="E20" s="14" t="s">
         <v>180</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="185.25" x14ac:dyDescent="0.45">
       <c r="A21" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="C21" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="D21" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="E21" s="14" t="s">
         <v>185</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="185.25" x14ac:dyDescent="0.45">
       <c r="A22" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="C22" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="D22" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="E22" s="14" t="s">
         <v>190</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A23" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="C23" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="D23" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="E23" s="14" t="s">
         <v>195</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
@@ -6840,110 +6840,110 @@
   <sheetData>
     <row r="3" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B3" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C4" t="s">
         <v>249</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>250</v>
-      </c>
-      <c r="D4" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D7" t="s">
         <v>253</v>
-      </c>
-      <c r="D7" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.45">
       <c r="H20" s="19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
+        <v>256</v>
+      </c>
+      <c r="C21" t="s">
+        <v>235</v>
+      </c>
+      <c r="D21" t="s">
         <v>257</v>
       </c>
-      <c r="C21" t="s">
-        <v>236</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>258</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>259</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>260</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>261</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>262</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>263</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>264</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>265</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>266</v>
-      </c>
-      <c r="M21" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
+        <v>267</v>
+      </c>
+      <c r="C22" t="s">
         <v>268</v>
       </c>
-      <c r="C22" t="s">
-        <v>269</v>
-      </c>
       <c r="E22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -6955,12 +6955,12 @@
         <v>5</v>
       </c>
       <c r="M22" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.45">
       <c r="G23" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J23">
         <v>-1</v>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB90C42-B5A5-4CA1-9F30-F34DDE91013A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8504B507-765E-496B-979F-05BEDAFA8EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
+    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="6" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
   <sheets>
     <sheet name="veda input" sheetId="1" r:id="rId1"/>
@@ -68,24 +68,6 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={34ED3C89-69D4-4FF1-94CC-CE0D879943AA}</author>
-  </authors>
-  <commentList>
-    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{34ED3C89-69D4-4FF1-94CC-CE0D879943AA}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    CAP (nonRE) &gt; COMPRD (DEF_C) </t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="278">
   <si>
@@ -2792,9 +2774,6 @@
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
   <si>
-    <t>~UC_T: LO</t>
-  </si>
-  <si>
     <t>UC_N</t>
   </si>
   <si>
@@ -2859,6 +2838,9 @@
   </si>
   <si>
     <t>Supercritical Coal, IGCC, coal_ccs</t>
+  </si>
+  <si>
+    <t>~UC_T: LO~2030</t>
   </si>
 </sst>
 </file>
@@ -3128,9 +3110,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="黄 凱凱(Kaikai Huang)" id="{9D5651AD-03AB-49CF-BE42-59AD7CA83975}" userId="S::J2412140@jera.co.jp::f9b6adb6-b751-4da6-9b6e-314b902b48bf" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3428,14 +3408,6 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="H20" dT="2026-04-17T06:07:36.14" personId="{9D5651AD-03AB-49CF-BE42-59AD7CA83975}" id="{34ED3C89-69D4-4FF1-94CC-CE0D879943AA}">
-    <text xml:space="preserve">CAP (nonRE) &gt; COMPRD (DEF_C) </text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75F77616-F3F2-4CAD-9718-D78F2778A52A}">
   <dimension ref="B2:S18"/>
@@ -4153,7 +4125,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="H15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>83</v>
@@ -4304,7 +4276,7 @@
         <v>19</v>
       </c>
       <c r="D18" s="15">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="15">
         <v>0.5</v>
@@ -4319,7 +4291,7 @@
       <c r="I18" s="15"/>
       <c r="J18" s="15"/>
       <c r="K18" s="20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L18" s="20">
         <f>L6</f>
@@ -6829,7 +6801,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F268AA5-7930-4A9B-8922-4C67ECE05AA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F268AA5-7930-4A9B-8922-4C67ECE05AA1}">
   <dimension ref="B3:M23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -6856,7 +6828,7 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C5" t="s">
         <v>252</v>
@@ -6867,10 +6839,10 @@
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D6" t="s">
         <v>251</v>
@@ -6878,7 +6850,7 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C7" t="s">
         <v>252</v>
@@ -6894,56 +6866,56 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.45">
       <c r="H20" s="19" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C21" t="s">
         <v>235</v>
       </c>
       <c r="D21" t="s">
+        <v>256</v>
+      </c>
+      <c r="E21" t="s">
         <v>257</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>258</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>259</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>260</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>261</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>262</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>263</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>264</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>265</v>
-      </c>
-      <c r="M21" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
+        <v>266</v>
+      </c>
+      <c r="C22" t="s">
         <v>267</v>
       </c>
-      <c r="C22" t="s">
-        <v>268</v>
-      </c>
       <c r="E22" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -6955,12 +6927,12 @@
         <v>5</v>
       </c>
       <c r="M22" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.45">
       <c r="G23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -6968,6 +6940,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_advanced_features.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8504B507-765E-496B-979F-05BEDAFA8EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0A4705-7F21-4329-9A64-2A4CEEA16E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="6" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
   <sheets>
     <sheet name="veda input" sheetId="1" r:id="rId1"/>
@@ -3107,10 +3107,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4329,7 +4325,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA60F42B-F2D1-44E2-B5F0-15531EB389CB}">
-  <dimension ref="B2:AX26"/>
+  <dimension ref="B2:BC26"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
@@ -4374,7 +4370,7 @@
     <col min="49" max="50" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:50" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:55" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="16" t="s">
         <v>199</v>
       </c>
@@ -4382,7 +4378,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="2:50" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:55" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B3" t="s">
         <v>201</v>
       </c>
@@ -4475,51 +4471,91 @@
         <v>41</v>
       </c>
       <c r="AI3" s="3">
-        <f t="shared" si="0"/>
+        <f>AH3+20-2</f>
+        <v>59</v>
+      </c>
+      <c r="AJ3" s="3">
+        <f>AI3+1</f>
+        <v>60</v>
+      </c>
+      <c r="AK3" s="3">
+        <f>AJ3+1</f>
+        <v>61</v>
+      </c>
+      <c r="AL3" s="3">
+        <f>AK3+20-2</f>
         <v>79</v>
       </c>
-      <c r="AJ3" s="3">
-        <f t="shared" si="0"/>
+      <c r="AM3" s="3">
+        <f>AL3+1</f>
         <v>80</v>
       </c>
-      <c r="AK3" s="3">
-        <f t="shared" si="0"/>
+      <c r="AN3" s="3">
+        <f>AM3+1</f>
         <v>81</v>
       </c>
-      <c r="AL3" s="3">
-        <f t="shared" si="0"/>
+      <c r="AO3" s="3">
+        <f>AN3+20-2</f>
+        <v>99</v>
+      </c>
+      <c r="AP3" s="3">
+        <f>AO3+1</f>
+        <v>100</v>
+      </c>
+      <c r="AQ3" s="3">
+        <f>AP3+1</f>
+        <v>101</v>
+      </c>
+      <c r="AR3" s="3">
+        <f>AQ3+20-2</f>
         <v>119</v>
       </c>
-      <c r="AM3" s="3">
-        <f t="shared" si="0"/>
+      <c r="AS3" s="3">
+        <f>AR3+1</f>
         <v>120</v>
       </c>
-      <c r="AN3" s="3">
-        <f t="shared" si="0"/>
+      <c r="AT3" s="3">
+        <f>AS3+1</f>
         <v>121</v>
       </c>
-      <c r="AO3" s="3">
-        <f t="shared" si="0"/>
+      <c r="AU3" s="3">
+        <f>AT3+20-2</f>
+        <v>139</v>
+      </c>
+      <c r="AV3" s="3">
+        <f>AU3+1</f>
+        <v>140</v>
+      </c>
+      <c r="AW3" s="3">
+        <f>AV3+1</f>
+        <v>141</v>
+      </c>
+      <c r="AX3" s="3">
+        <f>AW3+20-2</f>
         <v>159</v>
       </c>
-      <c r="AP3" s="3">
-        <f t="shared" si="0"/>
+      <c r="AY3" s="3">
+        <f>AX3+1</f>
         <v>160</v>
       </c>
-      <c r="AQ3" s="3">
-        <f t="shared" si="0"/>
+      <c r="AZ3" s="3">
+        <f>AY3+1</f>
         <v>161</v>
       </c>
-      <c r="AR3" s="3">
-        <f t="shared" si="0"/>
-        <v>199</v>
-      </c>
-      <c r="AS3" s="3">
-        <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="4" spans="2:50" x14ac:dyDescent="0.45">
+      <c r="BA3" s="3">
+        <f>AZ3+20-2</f>
+        <v>179</v>
+      </c>
+      <c r="BB3" s="3">
+        <f>BA3+1</f>
+        <v>180</v>
+      </c>
+      <c r="BC3" s="3">
+        <f>BB3+1</f>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="2:55" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>211</v>
       </c>
@@ -4656,8 +4692,48 @@
         <f t="shared" si="0"/>
         <v>6.18</v>
       </c>
-    </row>
-    <row r="5" spans="2:50" x14ac:dyDescent="0.45">
+      <c r="AT4">
+        <f>AN4</f>
+        <v>1</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" ref="AU4:AU5" si="2">AO4</f>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" ref="AV4:AV5" si="3">AP4</f>
+        <v>6.18</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" ref="AW4:AW5" si="4">AQ4</f>
+        <v>1</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" ref="AX4:AX5" si="5">AR4</f>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" ref="AY4:AY5" si="6">AS4</f>
+        <v>6.18</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" ref="AZ4:AZ5" si="7">AT4</f>
+        <v>1</v>
+      </c>
+      <c r="BA4">
+        <f t="shared" ref="BA4:BA5" si="8">AU4</f>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="BB4">
+        <f t="shared" ref="BB4:BB5" si="9">AV4</f>
+        <v>6.18</v>
+      </c>
+      <c r="BC4">
+        <f t="shared" ref="BC4:BC5" si="10">AW4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:55" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>216</v>
       </c>
@@ -4794,13 +4870,53 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="2:50" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="AT5">
+        <f t="shared" ref="AT5" si="11">AN5</f>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="2"/>
+        <v>1.48</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="5"/>
+        <v>1.48</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="BA5">
+        <f t="shared" si="8"/>
+        <v>1.48</v>
+      </c>
+      <c r="BB5">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+      <c r="BC5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:55" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AD7" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="2:50" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:55" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B8" t="s">
         <v>201</v>
       </c>
@@ -4886,87 +5002,87 @@
         <v>210</v>
       </c>
       <c r="AE8" s="3">
-        <f t="shared" ref="AE8:AT10" si="2">I8</f>
+        <f t="shared" ref="AE8:AT10" si="12">I8</f>
         <v>1</v>
       </c>
       <c r="AF8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>29</v>
       </c>
       <c r="AG8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="AH8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AI8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>59</v>
       </c>
       <c r="AJ8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>60</v>
       </c>
       <c r="AK8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>61</v>
       </c>
       <c r="AL8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>89</v>
       </c>
       <c r="AM8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>90</v>
       </c>
       <c r="AN8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>91</v>
       </c>
       <c r="AO8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>119</v>
       </c>
       <c r="AP8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>120</v>
       </c>
       <c r="AQ8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>121</v>
       </c>
       <c r="AR8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>149</v>
       </c>
       <c r="AS8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>150</v>
       </c>
       <c r="AT8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>151</v>
       </c>
       <c r="AU8" s="3">
-        <f t="shared" ref="AO8:AX10" si="3">Y8</f>
+        <f t="shared" ref="AO8:AX10" si="13">Y8</f>
         <v>179</v>
       </c>
       <c r="AV8" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>180</v>
       </c>
       <c r="AW8" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>181</v>
       </c>
       <c r="AX8" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="2:50" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:55" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>218</v>
       </c>
@@ -5049,91 +5165,91 @@
         <v>3.72</v>
       </c>
       <c r="AD9">
-        <f t="shared" ref="AD9:AD10" si="4">H9</f>
+        <f t="shared" ref="AD9:AD10" si="14">H9</f>
         <v>83</v>
       </c>
       <c r="AE9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AG9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>3.72</v>
       </c>
       <c r="AH9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AI9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AJ9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>3.72</v>
       </c>
       <c r="AK9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AM9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>3.72</v>
       </c>
       <c r="AN9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AO9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="AP9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>3.72</v>
       </c>
       <c r="AQ9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="AR9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="AS9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>3.72</v>
       </c>
       <c r="AT9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="AU9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="AV9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>3.72</v>
       </c>
       <c r="AW9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="AX9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>3.72</v>
       </c>
     </row>
-    <row r="10" spans="2:50" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:55" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>220</v>
       </c>
@@ -5216,110 +5332,110 @@
         <v>13.27</v>
       </c>
       <c r="AD10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>84</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AG10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>13.27</v>
       </c>
       <c r="AH10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AI10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AJ10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>13.27</v>
       </c>
       <c r="AK10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AL10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AM10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>13.27</v>
       </c>
       <c r="AN10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AO10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="AP10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>13.27</v>
       </c>
       <c r="AQ10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="AR10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="AS10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>13.27</v>
       </c>
       <c r="AT10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="AU10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="AV10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>13.27</v>
       </c>
       <c r="AW10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="AX10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>13.27</v>
       </c>
     </row>
-    <row r="13" spans="2:50" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:55" x14ac:dyDescent="0.45">
       <c r="B13" s="16" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="14" spans="2:50" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:55" x14ac:dyDescent="0.45">
       <c r="B14" s="18" t="s">
         <v>222</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
     </row>
-    <row r="15" spans="2:50" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:55" x14ac:dyDescent="0.45">
       <c r="B15" s="18" t="s">
         <v>223</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
     </row>
-    <row r="16" spans="2:50" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:55" x14ac:dyDescent="0.45">
       <c r="B16" s="18" t="s">
         <v>224</v>
       </c>
